--- a/MainTop/24.02.2026 Таня Озон/print_print_sorted.xlsx
+++ b/MainTop/24.02.2026 Таня Озон/print_print_sorted.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Max\Documents\GitHub\Ozon_upload\MainTop\24.02.2026 Таня Озон\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06ABBB31-9253-4FB6-903B-28CE2FF963D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DFE4252-7F59-4157-9562-5A09BFA5A003}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -432,7 +432,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -440,6 +440,9 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -745,8 +748,9 @@
   <dimension ref="A1:N97"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="48.28515625" customWidth="1"/>
-    <col min="2" max="11" width="6" customWidth="1"/>
+    <col min="1" max="1" width="19.42578125" customWidth="1"/>
+    <col min="2" max="10" width="8.85546875" customWidth="1"/>
+    <col min="11" max="11" width="6" customWidth="1"/>
     <col min="12" max="12" width="5.7109375" customWidth="1"/>
     <col min="14" max="14" width="4.7109375" customWidth="1"/>
   </cols>
@@ -755,31 +759,31 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
+      <c r="B1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="5" t="s">
         <v>9</v>
       </c>
       <c r="K1" s="1" t="s">
@@ -5021,5 +5025,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>